--- a/Reliability/project1/Model_Fitting_Evaluation.xlsx
+++ b/Reliability/project1/Model_Fitting_Evaluation.xlsx
@@ -465,22 +465,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7798673497296784</v>
+        <v>0.77986734972969</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03646546199188624</v>
+        <v>0.03646546199188622</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9295086020450491</v>
+        <v>0.929508602045048</v>
       </c>
       <c r="E2" t="n">
         <v>0.9962901171853311</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2267344495738763</v>
+        <v>-0.226734449573625</v>
       </c>
       <c r="G2" t="n">
-        <v>-48.98223541064716</v>
+        <v>-48.98223541064718</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -495,22 +495,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6124970948414218</v>
+        <v>0.6124970948413967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01199631758624298</v>
+        <v>0.01199631758624302</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9268902229358496</v>
+        <v>0.9268902229358524</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983699954991361</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.333588354739344</v>
+        <v>-4.333588354740041</v>
       </c>
       <c r="G3" t="n">
-        <v>-66.77048870561254</v>
+        <v>-66.77048870561249</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -525,22 +525,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3039982428711071</v>
+        <v>0.3039982428710891</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005161691474089156</v>
+        <v>0.005161691474089148</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9258305724540867</v>
+        <v>0.9258305724540911</v>
       </c>
       <c r="E4" t="n">
         <v>0.9985115287394905</v>
       </c>
       <c r="F4" t="n">
-        <v>-16.24246707957184</v>
+        <v>-16.24246707957285</v>
       </c>
       <c r="G4" t="n">
-        <v>-80.26385517038347</v>
+        <v>-80.26385517038349</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4602186225388511</v>
+        <v>0.4602186225388554</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03943576244891618</v>
+        <v>0.03943576244892048</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8792256953636255</v>
+        <v>0.8792256953636244</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9879601167781867</v>
+        <v>0.9879601167781855</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.192911812229303</v>
+        <v>-9.192911812229145</v>
       </c>
       <c r="G5" t="n">
-        <v>-47.72931516798258</v>
+        <v>-47.72931516798084</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -615,22 +615,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7562702071573701</v>
+        <v>0.7562702071573382</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03188476841515053</v>
+        <v>0.03188476841515052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9374496228230567</v>
+        <v>0.9374496228230593</v>
       </c>
       <c r="E7" t="n">
         <v>0.9970607959776936</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7490613463615148</v>
+        <v>-0.7490613463622342</v>
       </c>
       <c r="G7" t="n">
-        <v>-51.13002979791508</v>
+        <v>-51.13002979791509</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1912853495246004</v>
+        <v>0.1912853495245941</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03235032358999011</v>
+        <v>0.03235032358999432</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9548626466913326</v>
+        <v>0.9548626466913341</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9915154716472621</v>
+        <v>0.9915154716472609</v>
       </c>
       <c r="F8" t="n">
-        <v>-24.11781281707413</v>
+        <v>-24.11781281707469</v>
       </c>
       <c r="G8" t="n">
-        <v>-50.89810008485583</v>
+        <v>-50.89810008485375</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -675,22 +675,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1832512233086139</v>
+        <v>0.1832512233086173</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01733426528411269</v>
+        <v>0.0173342652841136</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9465115230794561</v>
+        <v>0.9465115230794552</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9941810472290599</v>
+        <v>0.9941810472290595</v>
       </c>
       <c r="F9" t="n">
-        <v>-24.84725346438433</v>
+        <v>-24.84725346438402</v>
       </c>
       <c r="G9" t="n">
-        <v>-60.88112134596902</v>
+        <v>-60.88112134596817</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -705,19 +705,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.406750156477971</v>
+        <v>0.4067501564779338</v>
       </c>
       <c r="C10" t="n">
-        <v>0.009836753039780353</v>
+        <v>0.009836753039780355</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9278925166263726</v>
+        <v>0.9278925166263792</v>
       </c>
       <c r="E10" t="n">
         <v>0.9980102662608927</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.29245451906001</v>
+        <v>-11.29245451906157</v>
       </c>
       <c r="G10" t="n">
         <v>-69.94607356806385</v>
@@ -735,22 +735,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9679477958331523</v>
+        <v>0.9679477958330267</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0262143544539213</v>
+        <v>0.02621435445392128</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9298070228919981</v>
+        <v>0.9298070228920072</v>
       </c>
       <c r="E11" t="n">
         <v>0.997856061920434</v>
       </c>
       <c r="F11" t="n">
-        <v>3.446188907567577</v>
+        <v>3.446188907565372</v>
       </c>
       <c r="G11" t="n">
-        <v>-54.26317021321332</v>
+        <v>-54.26317021321333</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.390905714139647</v>
+        <v>0.3909057141396639</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005761073114057203</v>
+        <v>0.005761073114057228</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9244255636900243</v>
+        <v>0.924425563690021</v>
       </c>
       <c r="E12" t="n">
         <v>0.9987259907608718</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.96791110252083</v>
+        <v>-11.9679111025201</v>
       </c>
       <c r="G12" t="n">
-        <v>-78.5061042736488</v>
+        <v>-78.50610427364873</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -795,22 +795,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5969686571337882</v>
+        <v>0.5969686571336582</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06682754412868977</v>
+        <v>0.06682754412869037</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8997433034615226</v>
+        <v>0.8997433034615444</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9872097968232814</v>
+        <v>0.9872097968232812</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.770141348879729</v>
+        <v>-4.770141348883429</v>
       </c>
       <c r="G13" t="n">
-        <v>-39.29023913874155</v>
+        <v>-39.29023913874141</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -825,22 +825,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5745647000028217</v>
+        <v>0.5745647000027742</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03867612709881381</v>
+        <v>0.03867612709879691</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9179763155730731</v>
+        <v>0.9179763155730799</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9938681941971838</v>
+        <v>0.9938681941971865</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.420423662124369</v>
+        <v>-5.420423662125772</v>
       </c>
       <c r="G14" t="n">
-        <v>-48.04052384193886</v>
+        <v>-48.04052384194586</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3167786157781278</v>
+        <v>0.3167786157780804</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0172838250953833</v>
+        <v>0.01728382509538462</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9347205009946156</v>
+        <v>0.9347205009946253</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9960696305499304</v>
+        <v>0.99606963054993</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.54238607434842</v>
+        <v>-15.54238607435096</v>
       </c>
       <c r="G15" t="n">
-        <v>-60.92774688665816</v>
+        <v>-60.92774688665693</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -885,22 +885,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2336014248278798</v>
+        <v>0.2336014248279145</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01336910337747299</v>
+        <v>0.01336910337747297</v>
       </c>
       <c r="D16" t="n">
-        <v>0.942509845605082</v>
+        <v>0.9425098456050734</v>
       </c>
       <c r="E16" t="n">
         <v>0.996298172210538</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.72036178640824</v>
+        <v>-20.72036178640571</v>
       </c>
       <c r="G16" t="n">
-        <v>-65.03694323816556</v>
+        <v>-65.03694323816559</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
